--- a/player_stats_all.xlsx
+++ b/player_stats_all.xlsx
@@ -1536,11 +1536,21 @@
           <t>POR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -1881,11 +1891,21 @@
       <c r="B29" t="n">
         <v>0</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -3911,11 +3931,21 @@
           <t>OKC</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
@@ -4766,11 +4796,21 @@
       <c r="B86" t="n">
         <v>0</v>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
@@ -5011,11 +5051,21 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
@@ -5050,11 +5100,21 @@
       <c r="B92" t="n">
         <v>0</v>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
@@ -5091,11 +5151,21 @@
           <t>TOR</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
@@ -5132,11 +5202,21 @@
           <t>TOT</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
@@ -5581,11 +5661,21 @@
           <t>TOT</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
@@ -5979,11 +6069,21 @@
           <t>OKC</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
@@ -6734,11 +6834,21 @@
           <t>BOS</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
@@ -7030,11 +7140,21 @@
           <t>TOT</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
@@ -7530,11 +7650,21 @@
           <t>POR</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
@@ -8385,11 +8515,21 @@
       <c r="B159" t="n">
         <v>0</v>
       </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
       <c r="H159" t="n">
         <v>0</v>
       </c>
@@ -8477,11 +8617,21 @@
           <t>POR</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
       <c r="H161" t="n">
         <v>0</v>
       </c>
@@ -8771,11 +8921,21 @@
       <c r="B167" t="n">
         <v>0</v>
       </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
       <c r="H167" t="n">
         <v>0</v>
       </c>
@@ -10187,11 +10347,21 @@
       <c r="B195" t="n">
         <v>0</v>
       </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
@@ -15734,11 +15904,21 @@
       <c r="B304" t="n">
         <v>0</v>
       </c>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
       <c r="H304" t="n">
         <v>0</v>
       </c>
@@ -15928,11 +16108,21 @@
           <t>TOT</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
       <c r="H308" t="n">
         <v>0</v>
       </c>
@@ -16222,11 +16412,21 @@
       <c r="B314" t="n">
         <v>0</v>
       </c>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
+      <c r="C314" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
       <c r="H314" t="n">
         <v>0</v>
       </c>
@@ -17536,11 +17736,21 @@
       <c r="B340" t="n">
         <v>0</v>
       </c>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
+      <c r="C340" t="n">
+        <v>0</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
       <c r="H340" t="n">
         <v>0</v>
       </c>
@@ -17728,11 +17938,21 @@
       <c r="B344" t="n">
         <v>0</v>
       </c>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
+      <c r="C344" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
       <c r="H344" t="n">
         <v>0</v>
       </c>
@@ -18024,11 +18244,21 @@
           <t>OKC</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
       <c r="H350" t="n">
         <v>0</v>
       </c>
@@ -18677,11 +18907,21 @@
           <t>CHI</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
+      <c r="C363" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+      <c r="F363" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
       <c r="H363" t="n">
         <v>0</v>
       </c>
@@ -19381,11 +19621,21 @@
           <t>TOT</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
+      <c r="C377" t="n">
+        <v>0</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
       <c r="H377" t="n">
         <v>0</v>
       </c>
@@ -19881,11 +20131,21 @@
           <t>OKC</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
+      <c r="C387" t="n">
+        <v>0</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
       <c r="H387" t="n">
         <v>0</v>
       </c>
@@ -20993,11 +21253,21 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr"/>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr"/>
+      <c r="C409" t="n">
+        <v>0</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>0</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0</v>
+      </c>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
       <c r="H409" t="n">
         <v>0</v>
       </c>
@@ -21491,11 +21761,21 @@
       <c r="B419" t="n">
         <v>0</v>
       </c>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
+      <c r="C419" t="n">
+        <v>0</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>0</v>
+      </c>
+      <c r="F419" t="n">
+        <v>0</v>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
       <c r="H419" t="n">
         <v>0</v>
       </c>
@@ -21940,11 +22220,21 @@
           <t>IND</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
+      <c r="C428" t="n">
+        <v>0</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>0</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
       <c r="H428" t="n">
         <v>0</v>
       </c>
@@ -24123,11 +24413,21 @@
           <t>OKC</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr"/>
-      <c r="D471" t="inlineStr"/>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr"/>
+      <c r="C471" t="n">
+        <v>0</v>
+      </c>
+      <c r="D471" t="n">
+        <v>0</v>
+      </c>
+      <c r="E471" t="n">
+        <v>0</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
       <c r="H471" t="n">
         <v>0</v>
       </c>
@@ -27324,11 +27624,21 @@
       <c r="B534" t="n">
         <v>0</v>
       </c>
-      <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
+      <c r="C534" t="n">
+        <v>0</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0</v>
+      </c>
+      <c r="E534" t="n">
+        <v>0</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G534" t="n">
+        <v>0</v>
+      </c>
       <c r="H534" t="n">
         <v>0</v>
       </c>
@@ -27465,11 +27775,21 @@
       <c r="B537" t="n">
         <v>0</v>
       </c>
-      <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
-      <c r="G537" t="inlineStr"/>
+      <c r="C537" t="n">
+        <v>0</v>
+      </c>
+      <c r="D537" t="n">
+        <v>0</v>
+      </c>
+      <c r="E537" t="n">
+        <v>0</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0</v>
+      </c>
       <c r="H537" t="n">
         <v>0</v>
       </c>
@@ -27557,11 +27877,21 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
+      <c r="C539" t="n">
+        <v>0</v>
+      </c>
+      <c r="D539" t="n">
+        <v>0</v>
+      </c>
+      <c r="E539" t="n">
+        <v>0</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0</v>
+      </c>
+      <c r="G539" t="n">
+        <v>0</v>
+      </c>
       <c r="H539" t="n">
         <v>0</v>
       </c>
@@ -27800,11 +28130,21 @@
       <c r="B544" t="n">
         <v>0</v>
       </c>
-      <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
-      <c r="G544" t="inlineStr"/>
+      <c r="C544" t="n">
+        <v>0</v>
+      </c>
+      <c r="D544" t="n">
+        <v>0</v>
+      </c>
+      <c r="E544" t="n">
+        <v>0</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" t="n">
+        <v>0</v>
+      </c>
       <c r="H544" t="n">
         <v>0</v>
       </c>
@@ -28759,11 +29099,21 @@
           <t>TOT</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
-      <c r="G563" t="inlineStr"/>
+      <c r="C563" t="n">
+        <v>0</v>
+      </c>
+      <c r="D563" t="n">
+        <v>0</v>
+      </c>
+      <c r="E563" t="n">
+        <v>0</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" t="n">
+        <v>0</v>
+      </c>
       <c r="H563" t="n">
         <v>0</v>
       </c>
@@ -29257,11 +29607,21 @@
       <c r="B573" t="n">
         <v>0</v>
       </c>
-      <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
-      <c r="G573" t="inlineStr"/>
+      <c r="C573" t="n">
+        <v>0</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0</v>
+      </c>
+      <c r="E573" t="n">
+        <v>0</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0</v>
+      </c>
+      <c r="G573" t="n">
+        <v>0</v>
+      </c>
       <c r="H573" t="n">
         <v>0</v>
       </c>
@@ -29451,11 +29811,21 @@
           <t>ORL</t>
         </is>
       </c>
-      <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
+      <c r="C577" t="n">
+        <v>0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0</v>
+      </c>
       <c r="H577" t="n">
         <v>0</v>
       </c>
@@ -29492,11 +29862,21 @@
           <t>OKC</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
-      <c r="G578" t="inlineStr"/>
+      <c r="C578" t="n">
+        <v>0</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0</v>
+      </c>
       <c r="H578" t="n">
         <v>0</v>
       </c>
@@ -29533,11 +29913,21 @@
           <t>NOP</t>
         </is>
       </c>
-      <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
-      <c r="G579" t="inlineStr"/>
+      <c r="C579" t="n">
+        <v>0</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0</v>
+      </c>
+      <c r="E579" t="n">
+        <v>0</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0</v>
+      </c>
+      <c r="G579" t="n">
+        <v>0</v>
+      </c>
       <c r="H579" t="n">
         <v>0</v>
       </c>
@@ -29574,11 +29964,21 @@
           <t>NYK</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
+      <c r="C580" t="n">
+        <v>0</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0</v>
+      </c>
+      <c r="E580" t="n">
+        <v>0</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" t="n">
+        <v>0</v>
+      </c>
       <c r="H580" t="n">
         <v>0</v>
       </c>
